--- a/tools/importer/reports/import-consumer-product.report.xlsx
+++ b/tools/importer/reports/import-consumer-product.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="712" uniqueCount="469">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="712" uniqueCount="470">
   <si>
     <t>_reportFile</t>
   </si>
@@ -52,7 +52,7 @@
     <t>legal</t>
   </si>
   <si>
-    <t>2026-06-19T00:48:59.693Z</t>
+    <t>2026-06-22T16:47:55.547Z</t>
   </si>
   <si>
     <t>404 Page Not Found</t>
@@ -70,7 +70,7 @@
     <t>content</t>
   </si>
   <si>
-    <t>2026-06-19T00:49:43.591Z</t>
+    <t>2026-06-22T15:55:21.180Z</t>
   </si>
   <si>
     <t>https://www.avg.com/en-us/activate-account</t>
@@ -79,199 +79,205 @@
     <t>avg/en-us/antitrack.report.json</t>
   </si>
   <si>
+    <t>["card-pricing","card-pricing","carousel-blog"]</t>
+  </si>
+  <si>
+    <t>avg/en-us/antitrack</t>
+  </si>
+  <si>
+    <t>consumer-product</t>
+  </si>
+  <si>
+    <t>2026-06-22T18:04:20.630Z</t>
+  </si>
+  <si>
+    <t>Anti-Tracking Software: Block &amp; Remove Cookies | AVG</t>
+  </si>
+  <si>
+    <t>https://www.avg.com/en-us/antitrack</t>
+  </si>
+  <si>
+    <t>avg/en-us/antivirus-business-edition.report.json</t>
+  </si>
+  <si>
+    <t>avg/en-us/antivirus-business-edition</t>
+  </si>
+  <si>
+    <t>business-product</t>
+  </si>
+  <si>
+    <t>2026-06-22T17:48:20.123Z</t>
+  </si>
+  <si>
+    <t>Business Antivirus Software | AVG</t>
+  </si>
+  <si>
+    <t>https://www.avg.com/en-us/antivirus-business-edition</t>
+  </si>
+  <si>
+    <t>avg/en-us/antivirus-for-android.report.json</t>
+  </si>
+  <si>
+    <t>["columns-feature","carousel-blog"]</t>
+  </si>
+  <si>
+    <t>avg/en-us/antivirus-for-android</t>
+  </si>
+  <si>
+    <t>2026-06-22T18:04:28.963Z</t>
+  </si>
+  <si>
+    <t>Free Antivirus App for Android | AVG Mobile Security</t>
+  </si>
+  <si>
+    <t>https://www.avg.com/en-us/antivirus-for-android</t>
+  </si>
+  <si>
+    <t>avg/en-us/avg-antivirus-for-mac.report.json</t>
+  </si>
+  <si>
+    <t>["promo-bar","carousel-blog"]</t>
+  </si>
+  <si>
+    <t>avg/en-us/avg-antivirus-for-mac</t>
+  </si>
+  <si>
+    <t>2026-06-22T18:05:22.664Z</t>
+  </si>
+  <si>
+    <t>Download Mac Antivirus Software | Free Virus Scanner | AVG</t>
+  </si>
+  <si>
+    <t>https://www.avg.com/en-us/avg-antivirus-for-mac</t>
+  </si>
+  <si>
+    <t>avg/en-us/avg-cleaner-for-mac-guide.report.json</t>
+  </si>
+  <si>
+    <t>avg/en-us/avg-cleaner-for-mac-guide</t>
+  </si>
+  <si>
+    <t>2026-06-22T18:06:15.816Z</t>
+  </si>
+  <si>
+    <t>Clean My Mac | Free Up Disk Space in 5 Easy Steps | AVG</t>
+  </si>
+  <si>
+    <t>https://www.avg.com/en-us/avg-cleaner-for-mac-guide</t>
+  </si>
+  <si>
+    <t>avg/en-us/avg-driver-updater.report.json</t>
+  </si>
+  <si>
+    <t>["card-pricing","card-pricing","columns-feature","carousel-blog"]</t>
+  </si>
+  <si>
+    <t>avg/en-us/avg-driver-updater</t>
+  </si>
+  <si>
+    <t>2026-06-22T18:07:09.375Z</t>
+  </si>
+  <si>
+    <t>Update Drivers Automatically | Download AVG Driver Updater</t>
+  </si>
+  <si>
+    <t>https://www.avg.com/en-us/avg-driver-updater</t>
+  </si>
+  <si>
+    <t>avg/en-us/avg-go-tech-support.report.json</t>
+  </si>
+  <si>
+    <t>avg/en-us/avg-go-tech-support</t>
+  </si>
+  <si>
+    <t>2026-06-22T15:55:34.428Z</t>
+  </si>
+  <si>
+    <t>Get Tech Support for Any Device | AVG Go | Free Diagnosis</t>
+  </si>
+  <si>
+    <t>https://www.avg.com/en-us/avg-go-tech-support</t>
+  </si>
+  <si>
+    <t>avg/en-us/avg-memory-cleaner.report.json</t>
+  </si>
+  <si>
+    <t>["hero-product","rating","columns-feature","carousel-blog"]</t>
+  </si>
+  <si>
+    <t>avg/en-us/avg-memory-cleaner</t>
+  </si>
+  <si>
+    <t>2026-06-22T18:08:02.672Z</t>
+  </si>
+  <si>
+    <t>Free Phone Cleaner | Clean up Android Phones &amp; Tablets | AVG</t>
+  </si>
+  <si>
+    <t>https://www.avg.com/en-us/avg-memory-cleaner</t>
+  </si>
+  <si>
+    <t>avg/en-us/avg-pctuneup.report.json</t>
+  </si>
+  <si>
+    <t>["promo-bar","hero-product","rating","card-pricing","columns-feature","carousel-blog"]</t>
+  </si>
+  <si>
+    <t>avg/en-us/avg-pctuneup</t>
+  </si>
+  <si>
+    <t>2026-06-22T18:08:10.222Z</t>
+  </si>
+  <si>
+    <t>PC Cleaner &amp; Tune Up | Download Trial | AVG</t>
+  </si>
+  <si>
+    <t>https://www.avg.com/en-us/avg-pctuneup</t>
+  </si>
+  <si>
+    <t>avg/en-us/avg-remover.report.json</t>
+  </si>
+  <si>
+    <t>avg/en-us/avg-remover</t>
+  </si>
+  <si>
+    <t>2026-06-22T18:09:04.435Z</t>
+  </si>
+  <si>
+    <t>Install AVG on your PC, Mac | AVG installation files</t>
+  </si>
+  <si>
+    <t>https://www.avg.com/en-us/avg-remover</t>
+  </si>
+  <si>
+    <t>avg/en-us/avg-tuneup-for-mac.report.json</t>
+  </si>
+  <si>
+    <t>["promo-bar","card-pricing","card-pricing","carousel-blog"]</t>
+  </si>
+  <si>
+    <t>avg/en-us/avg-tuneup-for-mac</t>
+  </si>
+  <si>
+    <t>2026-06-22T18:09:56.631Z</t>
+  </si>
+  <si>
+    <t>Mac Cleaner and TuneUp Utility | AVG TuneUp for Mac</t>
+  </si>
+  <si>
+    <t>https://www.avg.com/en-us/avg-tuneup-for-mac</t>
+  </si>
+  <si>
+    <t>avg/en-us/avg-tuneup-ios.report.json</t>
+  </si>
+  <si>
     <t>["carousel-blog"]</t>
   </si>
   <si>
-    <t>avg/en-us/antitrack</t>
-  </si>
-  <si>
-    <t>consumer-product</t>
-  </si>
-  <si>
-    <t>2026-06-19T00:49:34.117Z</t>
-  </si>
-  <si>
-    <t>Anti-Tracking Software: Block &amp; Remove Cookies | AVG</t>
-  </si>
-  <si>
-    <t>https://www.avg.com/en-us/antitrack</t>
-  </si>
-  <si>
-    <t>avg/en-us/antivirus-business-edition.report.json</t>
-  </si>
-  <si>
-    <t>avg/en-us/antivirus-business-edition</t>
-  </si>
-  <si>
-    <t>business-product</t>
-  </si>
-  <si>
-    <t>2026-06-19T00:48:59.031Z</t>
-  </si>
-  <si>
-    <t>Business Antivirus Software | AVG</t>
-  </si>
-  <si>
-    <t>https://www.avg.com/en-us/antivirus-business-edition</t>
-  </si>
-  <si>
-    <t>avg/en-us/antivirus-for-android.report.json</t>
-  </si>
-  <si>
-    <t>["columns-feature","carousel-blog"]</t>
-  </si>
-  <si>
-    <t>avg/en-us/antivirus-for-android</t>
-  </si>
-  <si>
-    <t>2026-06-19T00:50:26.919Z</t>
-  </si>
-  <si>
-    <t>Free Antivirus App for Android | AVG Mobile Security</t>
-  </si>
-  <si>
-    <t>https://www.avg.com/en-us/antivirus-for-android</t>
-  </si>
-  <si>
-    <t>avg/en-us/avg-antivirus-for-mac.report.json</t>
-  </si>
-  <si>
-    <t>["promo-bar","carousel-blog"]</t>
-  </si>
-  <si>
-    <t>avg/en-us/avg-antivirus-for-mac</t>
-  </si>
-  <si>
-    <t>2026-06-19T00:51:19.408Z</t>
-  </si>
-  <si>
-    <t>Download Mac Antivirus Software | Free Virus Scanner | AVG</t>
-  </si>
-  <si>
-    <t>https://www.avg.com/en-us/avg-antivirus-for-mac</t>
-  </si>
-  <si>
-    <t>avg/en-us/avg-cleaner-for-mac-guide.report.json</t>
-  </si>
-  <si>
-    <t>avg/en-us/avg-cleaner-for-mac-guide</t>
-  </si>
-  <si>
-    <t>2026-06-19T00:52:11.432Z</t>
-  </si>
-  <si>
-    <t>Clean My Mac | Free Up Disk Space in 5 Easy Steps | AVG</t>
-  </si>
-  <si>
-    <t>https://www.avg.com/en-us/avg-cleaner-for-mac-guide</t>
-  </si>
-  <si>
-    <t>avg/en-us/avg-driver-updater.report.json</t>
-  </si>
-  <si>
-    <t>avg/en-us/avg-driver-updater</t>
-  </si>
-  <si>
-    <t>2026-06-19T00:53:04.519Z</t>
-  </si>
-  <si>
-    <t>Update Drivers Automatically | Download AVG Driver Updater</t>
-  </si>
-  <si>
-    <t>https://www.avg.com/en-us/avg-driver-updater</t>
-  </si>
-  <si>
-    <t>avg/en-us/avg-go-tech-support.report.json</t>
-  </si>
-  <si>
-    <t>avg/en-us/avg-go-tech-support</t>
-  </si>
-  <si>
-    <t>2026-06-19T00:49:56.751Z</t>
-  </si>
-  <si>
-    <t>Get Tech Support for Any Device | AVG Go | Free Diagnosis</t>
-  </si>
-  <si>
-    <t>https://www.avg.com/en-us/avg-go-tech-support</t>
-  </si>
-  <si>
-    <t>avg/en-us/avg-memory-cleaner.report.json</t>
-  </si>
-  <si>
-    <t>["hero-product","rating","columns-feature","carousel-blog"]</t>
-  </si>
-  <si>
-    <t>avg/en-us/avg-memory-cleaner</t>
-  </si>
-  <si>
-    <t>2026-06-19T00:53:56.945Z</t>
-  </si>
-  <si>
-    <t>Free Phone Cleaner | Clean up Android Phones &amp; Tablets | AVG</t>
-  </si>
-  <si>
-    <t>https://www.avg.com/en-us/avg-memory-cleaner</t>
-  </si>
-  <si>
-    <t>avg/en-us/avg-pctuneup.report.json</t>
-  </si>
-  <si>
-    <t>["promo-bar","hero-product","rating","columns-feature","carousel-blog"]</t>
-  </si>
-  <si>
-    <t>avg/en-us/avg-pctuneup</t>
-  </si>
-  <si>
-    <t>2026-06-19T00:54:49.856Z</t>
-  </si>
-  <si>
-    <t>PC Cleaner &amp; Tune Up | Download Trial | AVG</t>
-  </si>
-  <si>
-    <t>https://www.avg.com/en-us/avg-pctuneup</t>
-  </si>
-  <si>
-    <t>avg/en-us/avg-remover.report.json</t>
-  </si>
-  <si>
-    <t>avg/en-us/avg-remover</t>
-  </si>
-  <si>
-    <t>2026-06-19T00:55:42.158Z</t>
-  </si>
-  <si>
-    <t>Install AVG on your PC, Mac | AVG installation files</t>
-  </si>
-  <si>
-    <t>https://www.avg.com/en-us/avg-remover</t>
-  </si>
-  <si>
-    <t>avg/en-us/avg-tuneup-for-mac.report.json</t>
-  </si>
-  <si>
-    <t>["promo-bar","card-pricing","carousel-blog"]</t>
-  </si>
-  <si>
-    <t>avg/en-us/avg-tuneup-for-mac</t>
-  </si>
-  <si>
-    <t>2026-06-19T00:56:34.921Z</t>
-  </si>
-  <si>
-    <t>Mac Cleaner and TuneUp Utility | AVG TuneUp for Mac</t>
-  </si>
-  <si>
-    <t>https://www.avg.com/en-us/avg-tuneup-for-mac</t>
-  </si>
-  <si>
-    <t>avg/en-us/avg-tuneup-ios.report.json</t>
-  </si>
-  <si>
     <t>avg/en-us/avg-tuneup-ios</t>
   </si>
   <si>
-    <t>2026-06-19T00:57:28.536Z</t>
+    <t>2026-06-22T18:10:53.126Z</t>
   </si>
   <si>
     <t>Free iPhone &amp; iPad Cleaner | Clean Your iOS Storage</t>
@@ -289,7 +295,7 @@
     <t>free-tool</t>
   </si>
   <si>
-    <t>2026-06-19T00:49:44.368Z</t>
+    <t>2026-06-22T17:58:41.098Z</t>
   </si>
   <si>
     <t>Awards | Reviews and Awards | Antivirus and Security Software</t>
@@ -304,7 +310,7 @@
     <t>avg/en-us/battery-saver-for-windows</t>
   </si>
   <si>
-    <t>2026-06-19T00:57:36.433Z</t>
+    <t>2026-06-22T18:11:49.609Z</t>
   </si>
   <si>
     <t>Battery Saver for Laptops with Windows 10, 8, 8.1 and 7 | AVG</t>
@@ -319,7 +325,7 @@
     <t>avg/en-us/beta</t>
   </si>
   <si>
-    <t>2026-06-19T00:49:07.649Z</t>
+    <t>2026-06-22T16:48:02.524Z</t>
   </si>
   <si>
     <t>Compare AVG Beta Products | Find the Perfect Software</t>
@@ -334,7 +340,7 @@
     <t>avg/en-us/breachguard</t>
   </si>
   <si>
-    <t>2026-06-19T00:58:30.155Z</t>
+    <t>2026-06-22T18:12:46.551Z</t>
   </si>
   <si>
     <t>Data Breach &amp; Leak Prevention Software | AVG BreachGuard</t>
@@ -349,7 +355,7 @@
     <t>avg/en-us/business-events-and-webinars</t>
   </si>
   <si>
-    <t>2026-06-19T00:49:06.024Z</t>
+    <t>2026-06-22T17:49:13.465Z</t>
   </si>
   <si>
     <t>AVG Business Reseller Webinars | Learn About IT Services</t>
@@ -364,7 +370,7 @@
     <t>avg/en-us/business-resources</t>
   </si>
   <si>
-    <t>2026-06-19T00:49:58.132Z</t>
+    <t>2026-06-22T17:50:07.569Z</t>
   </si>
   <si>
     <t>AVG Business Resources | PDFs, Case Studies and Videos</t>
@@ -376,13 +382,13 @@
     <t>avg/en-us/business-security.report.json</t>
   </si>
   <si>
-    <t>["hero","comparison-matrix","teaser-cta","columns","columns-feature"]</t>
+    <t>["hero","comparison-matrix","teaser-cta","columns","columns-feature","card"]</t>
   </si>
   <si>
     <t>avg/en-us/business-security</t>
   </si>
   <si>
-    <t>2026-06-19T00:50:50.665Z</t>
+    <t>2026-06-22T17:50:59.816Z</t>
   </si>
   <si>
     <t>AVG Business Security Solutions for Small Businesses</t>
@@ -397,7 +403,7 @@
     <t>avg/en-us/cancellation-refund-policy</t>
   </si>
   <si>
-    <t>2026-06-19T00:49:15.121Z</t>
+    <t>2026-06-22T16:48:08.805Z</t>
   </si>
   <si>
     <t>AVG | Your Right to Refund any AVG product</t>
@@ -412,7 +418,7 @@
     <t>avg/en-us/consent-policy</t>
   </si>
   <si>
-    <t>2026-06-19T00:50:08.007Z</t>
+    <t>2026-06-22T16:49:01.458Z</t>
   </si>
   <si>
     <t>Consent Policy | We are serious about your privacy | AVG</t>
@@ -427,7 +433,7 @@
     <t>avg/en-us/contacts</t>
   </si>
   <si>
-    <t>2026-06-19T00:51:01.319Z</t>
+    <t>2026-06-22T15:56:40.465Z</t>
   </si>
   <si>
     <t>Contact Us | AVG</t>
@@ -442,7 +448,7 @@
     <t>avg/en-us/cookies</t>
   </si>
   <si>
-    <t>2026-06-19T00:51:01.282Z</t>
+    <t>2026-06-22T16:49:55.931Z</t>
   </si>
   <si>
     <t>Cookies Policy | We are serious about your privacy | AVG</t>
@@ -457,7 +463,7 @@
     <t>avg/en-us/do-not-sell</t>
   </si>
   <si>
-    <t>2026-06-19T00:51:07.462Z</t>
+    <t>2026-06-22T16:50:48.557Z</t>
   </si>
   <si>
     <t>Do Not Sell or Share My Info | AVG</t>
@@ -475,7 +481,7 @@
     <t>avg/en-us/download-secure-vpn-android</t>
   </si>
   <si>
-    <t>2026-06-19T00:59:24.037Z</t>
+    <t>2026-06-22T18:13:40.323Z</t>
   </si>
   <si>
     <t>VPN For Android | Download Free Trial | AVG Secure VPN</t>
@@ -490,7 +496,7 @@
     <t>avg/en-us/download-secure-vpn-ios</t>
   </si>
   <si>
-    <t>2026-06-19T01:00:16.096Z</t>
+    <t>2026-06-22T18:15:33.366Z</t>
   </si>
   <si>
     <t>Download a Free Trial of AVG VPN For iOS | AVG Secure VPN</t>
@@ -502,13 +508,13 @@
     <t>avg/en-us/download-secure-vpn-mac.report.json</t>
   </si>
   <si>
-    <t>["promo-bar","columns-feature","carousel-blog"]</t>
+    <t>["promo-bar","card-pricing","card-pricing","columns-feature","carousel-blog"]</t>
   </si>
   <si>
     <t>avg/en-us/download-secure-vpn-mac</t>
   </si>
   <si>
-    <t>2026-06-19T01:01:10.271Z</t>
+    <t>2026-06-22T18:15:40.192Z</t>
   </si>
   <si>
     <t>Free VPN Download for Mac</t>
@@ -526,7 +532,7 @@
     <t>avg/en-us/email-server-business-edition</t>
   </si>
   <si>
-    <t>2026-06-19T00:51:43.113Z</t>
+    <t>2026-06-22T17:51:51.021Z</t>
   </si>
   <si>
     <t>AVG Email Server Security | Antivirus &amp; Antispam | Free Trial</t>
@@ -541,7 +547,7 @@
     <t>avg/en-us/endpoint-protection</t>
   </si>
   <si>
-    <t>2026-06-19T00:52:35.601Z</t>
+    <t>2026-06-22T17:52:43.099Z</t>
   </si>
   <si>
     <t>Endpoint protection for business | AVG</t>
@@ -556,7 +562,7 @@
     <t>avg/en-us/eula</t>
   </si>
   <si>
-    <t>2026-06-19T00:52:01.180Z</t>
+    <t>2026-06-22T16:51:41.277Z</t>
   </si>
   <si>
     <t>End user license agreements | AVG</t>
@@ -568,13 +574,10 @@
     <t>avg/en-us/file-server-business-edition.report.json</t>
   </si>
   <si>
-    <t>["teaser-cta","card"]</t>
-  </si>
-  <si>
     <t>avg/en-us/file-server-business-edition</t>
   </si>
   <si>
-    <t>2026-06-19T00:53:27.882Z</t>
+    <t>2026-06-22T17:52:50.447Z</t>
   </si>
   <si>
     <t>Windows Server AntiVirus &amp; Network Security | AVG Business</t>
@@ -589,7 +592,7 @@
     <t>avg/en-us/free-antivirus-download</t>
   </si>
   <si>
-    <t>2026-06-19T01:02:03.863Z</t>
+    <t>2026-06-22T18:16:33.648Z</t>
   </si>
   <si>
     <t>Download Free Antivirus Software for PC | AVG Virus Protection</t>
@@ -604,7 +607,7 @@
     <t>avg/en-us/hackers-and-hacking</t>
   </si>
   <si>
-    <t>2026-06-19T00:51:54.161Z</t>
+    <t>2026-06-22T15:57:33.423Z</t>
   </si>
   <si>
     <t>Hackers and Hacking | Free eBook from AVG SMB</t>
@@ -622,7 +625,7 @@
     <t>avg/en-us/help-me-choose</t>
   </si>
   <si>
-    <t>2026-06-19T00:50:38.480Z</t>
+    <t>2026-06-22T17:59:34.568Z</t>
   </si>
   <si>
     <t>Find an AVG Product with our Interactive Tool | Try it Now</t>
@@ -658,7 +661,7 @@
     <t>avg/en-us/internet-security-be-demo</t>
   </si>
   <si>
-    <t>2026-06-19T01:03:02.749Z</t>
+    <t>2026-06-22T18:17:34.336Z</t>
   </si>
   <si>
     <t>AVG Business Internet Security | Online Security for Businesses</t>
@@ -673,7 +676,7 @@
     <t>avg/en-us/internet-security-business-edition</t>
   </si>
   <si>
-    <t>2026-06-19T00:54:19.791Z</t>
+    <t>2026-06-22T17:53:43.722Z</t>
   </si>
   <si>
     <t>Business Cybersecurity Solution | AVG</t>
@@ -688,7 +691,7 @@
     <t>avg/en-us/internet-security-for-mac</t>
   </si>
   <si>
-    <t>2026-06-19T01:03:56.196Z</t>
+    <t>2026-06-22T18:18:28.377Z</t>
   </si>
   <si>
     <t>AVG Internet Security for Mac | Mac Security Software</t>
@@ -703,7 +706,7 @@
     <t>avg/en-us/internet-security</t>
   </si>
   <si>
-    <t>2026-06-19T01:02:10.228Z</t>
+    <t>2026-06-22T18:17:26.955Z</t>
   </si>
   <si>
     <t>AVG Internet Security Software | Online Protection | Free Trial</t>
@@ -718,7 +721,7 @@
     <t>avg/en-us/keeping-your-data-safe</t>
   </si>
   <si>
-    <t>2026-06-19T00:52:00.998Z</t>
+    <t>2026-06-22T15:57:39.680Z</t>
   </si>
   <si>
     <t>Keeping Your Data Safe | Free eBook from AVG SMB</t>
@@ -733,7 +736,7 @@
     <t>avg/en-us/legal-documentation</t>
   </si>
   <si>
-    <t>2026-06-19T00:52:52.920Z</t>
+    <t>2026-06-22T16:52:34.671Z</t>
   </si>
   <si>
     <t>AVG | Supporting contract documentation</t>
@@ -751,7 +754,7 @@
     <t>avg/en-us/management-console</t>
   </si>
   <si>
-    <t>2026-06-19T00:55:11.492Z</t>
+    <t>2026-06-22T17:54:35.741Z</t>
   </si>
   <si>
     <t>Cloud Management Console - Antivirus Security from the Cloud | AVG</t>
@@ -766,7 +769,7 @@
     <t>avg/en-us/mobile-security-for-iphone-ipad</t>
   </si>
   <si>
-    <t>2026-06-19T01:04:49.757Z</t>
+    <t>2026-06-22T18:19:21.416Z</t>
   </si>
   <si>
     <t>Free Antivirus App for iPhone and iPad | AVG Mobile Security</t>
@@ -781,7 +784,7 @@
     <t>avg/en-us/online-markets-by-country</t>
   </si>
   <si>
-    <t>2026-06-19T00:51:31.068Z</t>
+    <t>2026-06-22T18:00:28.391Z</t>
   </si>
   <si>
     <t>AVG | Trading without borders: Global Internet usage statistics by country</t>
@@ -799,7 +802,7 @@
     <t>avg/en-us/online-research-faq</t>
   </si>
   <si>
-    <t>2026-06-19T00:52:24.471Z</t>
+    <t>2026-06-22T18:01:20.528Z</t>
   </si>
   <si>
     <t>AVG | Online Research</t>
@@ -817,7 +820,7 @@
     <t>avg/en-us/online-research-main</t>
   </si>
   <si>
-    <t>2026-06-19T00:53:16.364Z</t>
+    <t>2026-06-22T18:02:13.107Z</t>
   </si>
   <si>
     <t>https://www.avg.com/en-us/online-research-main</t>
@@ -829,7 +832,7 @@
     <t>avg/en-us/online-security-plugin</t>
   </si>
   <si>
-    <t>2026-06-19T00:52:54.193Z</t>
+    <t>2026-06-22T15:58:33.050Z</t>
   </si>
   <si>
     <t>AVG Online Security Plugin | Free Browser Security Extension</t>
@@ -844,7 +847,7 @@
     <t>avg/en-us/partners</t>
   </si>
   <si>
-    <t>2026-06-19T00:53:46.999Z</t>
+    <t>2026-06-22T15:59:25.738Z</t>
   </si>
   <si>
     <t>Partner with the Global Leader in Security | AVG Business</t>
@@ -859,7 +862,7 @@
     <t>avg/en-us/patch-management</t>
   </si>
   <si>
-    <t>2026-06-19T00:56:03.159Z</t>
+    <t>2026-06-22T17:55:28.070Z</t>
   </si>
   <si>
     <t>Business Patch Management for Windows | AVG</t>
@@ -874,7 +877,7 @@
     <t>avg/en-us/policies</t>
   </si>
   <si>
-    <t>2026-06-19T00:53:44.897Z</t>
+    <t>2026-06-22T16:52:46.157Z</t>
   </si>
   <si>
     <t>Terms &amp; Policies | AVG</t>
@@ -889,7 +892,7 @@
     <t>avg/en-us/privacy-preferences</t>
   </si>
   <si>
-    <t>2026-06-19T00:55:30.091Z</t>
+    <t>2026-06-22T16:53:43.934Z</t>
   </si>
   <si>
     <t>Privacy Preferences</t>
@@ -904,7 +907,7 @@
     <t>avg/en-us/privacy</t>
   </si>
   <si>
-    <t>2026-06-19T00:54:36.512Z</t>
+    <t>2026-06-22T16:52:52.555Z</t>
   </si>
   <si>
     <t>Privacy Policy | We are serious about your privacy | Avast</t>
@@ -919,7 +922,7 @@
     <t>avg/en-us/products-policy</t>
   </si>
   <si>
-    <t>2026-06-19T00:57:16.919Z</t>
+    <t>2026-06-22T16:55:31.907Z</t>
   </si>
   <si>
     <t>Products Policy | We are serious about your privacy | AVG</t>
@@ -934,7 +937,7 @@
     <t>avg/en-us/profile</t>
   </si>
   <si>
-    <t>2026-06-19T00:54:40.227Z</t>
+    <t>2026-06-22T16:00:17.051Z</t>
   </si>
   <si>
     <t>Profile | AVG Technologies</t>
@@ -946,13 +949,13 @@
     <t>avg/en-us/random-password-generator.report.json</t>
   </si>
   <si>
-    <t>["promo-bar","tool-placeholder","card-feature","accordion-faq","accordion-faq"]</t>
+    <t>["promo-bar","tool-placeholder","card","card-feature","accordion-faq","accordion-faq"]</t>
   </si>
   <si>
     <t>avg/en-us/random-password-generator</t>
   </si>
   <si>
-    <t>2026-06-19T00:54:09.140Z</t>
+    <t>2026-06-22T18:03:06.183Z</t>
   </si>
   <si>
     <t>Random Password Generator | Free Online Tool | AVG</t>
@@ -967,7 +970,7 @@
     <t>avg/en-us/ransomware-decryption-tools</t>
   </si>
   <si>
-    <t>2026-06-19T00:55:02.215Z</t>
+    <t>2026-06-22T18:03:59.467Z</t>
   </si>
   <si>
     <t>Free Ransomware Decryption Tools | Unlock Your Files | AVG</t>
@@ -982,7 +985,7 @@
     <t>avg/en-us/remote-access-terms-and-conditions</t>
   </si>
   <si>
-    <t>2026-06-19T00:58:09.460Z</t>
+    <t>2026-06-22T16:56:24.509Z</t>
   </si>
   <si>
     <t>Consent to remote access | AVG</t>
@@ -997,7 +1000,7 @@
     <t>avg/en-us/remove-win32-expiro</t>
   </si>
   <si>
-    <t>2026-06-19T00:55:34.164Z</t>
+    <t>2026-06-22T16:01:11.649Z</t>
   </si>
   <si>
     <t>How to Remove Win32/Expiro in 3 Easy Steps | AVG</t>
@@ -1012,7 +1015,7 @@
     <t>avg/en-us/remove-win32-neshta</t>
   </si>
   <si>
-    <t>2026-06-19T00:56:27.932Z</t>
+    <t>2026-06-22T16:02:03.937Z</t>
   </si>
   <si>
     <t>How to Remove Win32/Neshta in 3 Easy Steps | AVG</t>
@@ -1027,7 +1030,7 @@
     <t>avg/en-us/remove-win32-virut</t>
   </si>
   <si>
-    <t>2026-06-19T00:57:20.566Z</t>
+    <t>2026-06-22T16:02:56.968Z</t>
   </si>
   <si>
     <t>How to Remove Win32/Virut in 3 Easy Steps | AVG</t>
@@ -1042,7 +1045,7 @@
     <t>avg/en-us/research-participant-terms-conditions</t>
   </si>
   <si>
-    <t>2026-06-19T00:59:01.864Z</t>
+    <t>2026-06-22T16:57:18.478Z</t>
   </si>
   <si>
     <t>Research Participant Terms and Conditions | AVG</t>
@@ -1057,7 +1060,7 @@
     <t>avg/en-us/secure-browser</t>
   </si>
   <si>
-    <t>2026-06-19T01:05:43.279Z</t>
+    <t>2026-06-22T18:20:14.020Z</t>
   </si>
   <si>
     <t>Download Our Free Private Web Browser | AVG Secure Browser</t>
@@ -1072,7 +1075,7 @@
     <t>avg/en-us/secure-vpn-acceptable-use</t>
   </si>
   <si>
-    <t>2026-06-19T00:59:54.993Z</t>
+    <t>2026-06-22T16:58:10.501Z</t>
   </si>
   <si>
     <t>AVG | Secure VPN Acceptable Use</t>
@@ -1090,7 +1093,7 @@
     <t>avg/en-us/secure-vpn</t>
   </si>
   <si>
-    <t>2026-06-19T01:06:36.407Z</t>
+    <t>2026-06-22T17:47:03.691Z</t>
   </si>
   <si>
     <t>Download Secure VPN for PC or Laptop | Free Trial | AVG</t>
@@ -1105,7 +1108,7 @@
     <t>avg/en-us/services</t>
   </si>
   <si>
-    <t>2026-06-19T00:58:13.151Z</t>
+    <t>2026-06-22T16:03:50.431Z</t>
   </si>
   <si>
     <t>https://www.avg.com/en-us/services</t>
@@ -1117,7 +1120,7 @@
     <t>avg/en-us/small-business-digital-policy-guide-download</t>
   </si>
   <si>
-    <t>2026-06-19T00:56:56.463Z</t>
+    <t>2026-06-22T17:56:21.028Z</t>
   </si>
   <si>
     <t>Small Business Digital Policy Guide | Free eBook from AVG SMB</t>
@@ -1132,7 +1135,7 @@
     <t>avg/en-us/store-business</t>
   </si>
   <si>
-    <t>2026-06-19T00:57:48.108Z</t>
+    <t>2026-06-22T17:57:14.041Z</t>
   </si>
   <si>
     <t>AVG Business Products | Explore AVG business security solutions</t>
@@ -1147,7 +1150,7 @@
     <t>avg/en-us/store</t>
   </si>
   <si>
-    <t>2026-06-19T01:07:29.540Z</t>
+    <t>2026-06-22T18:21:08.860Z</t>
   </si>
   <si>
     <t>AVG Store | Explore all Products &amp; Prices | Buy AVG Now!</t>
@@ -1162,7 +1165,7 @@
     <t>avg/en-us/submit-a-sample</t>
   </si>
   <si>
-    <t>2026-06-19T00:59:04.654Z</t>
+    <t>2026-06-22T16:04:42.160Z</t>
   </si>
   <si>
     <t>Choose Your Sample Submission Type | AVG</t>
@@ -1177,7 +1180,7 @@
     <t>avg/en-us/subscription-details</t>
   </si>
   <si>
-    <t>2026-06-19T01:00:47.165Z</t>
+    <t>2026-06-22T17:02:12.367Z</t>
   </si>
   <si>
     <t>Subscription details</t>
@@ -1192,7 +1195,7 @@
     <t>avg/en-us/supplier-guidelines</t>
   </si>
   <si>
-    <t>2026-06-19T01:01:48.946Z</t>
+    <t>2026-06-22T17:03:58.572Z</t>
   </si>
   <si>
     <t>AVG Supplier Guidelines</t>
@@ -1207,7 +1210,7 @@
     <t>avg/en-us/supplier</t>
   </si>
   <si>
-    <t>2026-06-19T01:01:40.084Z</t>
+    <t>2026-06-22T17:03:06.033Z</t>
   </si>
   <si>
     <t>AVG | Supporting supplier documentation</t>
@@ -1222,7 +1225,7 @@
     <t>avg/en-us/trademarks</t>
   </si>
   <si>
-    <t>2026-06-19T01:02:42.330Z</t>
+    <t>2026-06-22T17:04:52.203Z</t>
   </si>
   <si>
     <t>Third Party Copyrights &amp; Trademarks</t>
@@ -1237,7 +1240,7 @@
     <t>avg/en-us/tuneup-software-updater</t>
   </si>
   <si>
-    <t>2026-06-19T01:08:22.126Z</t>
+    <t>2026-06-22T18:22:01.664Z</t>
   </si>
   <si>
     <t>Update Software Automatically | AVG Software Updater for PC</t>
@@ -1252,7 +1255,7 @@
     <t>avg/en-us/ultimate</t>
   </si>
   <si>
-    <t>2026-06-19T01:09:15.715Z</t>
+    <t>2026-06-22T18:22:55.035Z</t>
   </si>
   <si>
     <t>AVG Ultimate | Multi-device Antivirus, Performance &amp; VPN Bundle</t>
@@ -1267,7 +1270,7 @@
     <t>avg/en-us/vpn-dmca</t>
   </si>
   <si>
-    <t>2026-06-19T01:03:37.095Z</t>
+    <t>2026-06-22T17:05:45.153Z</t>
   </si>
   <si>
     <t>DMCA | AVG Safe Surf</t>
@@ -1282,7 +1285,7 @@
     <t>avg/en-us/vpn-policy</t>
   </si>
   <si>
-    <t>2026-06-19T01:04:28.877Z</t>
+    <t>2026-06-22T17:06:36.209Z</t>
   </si>
   <si>
     <t>VPN Policy | We are serious about your privacy | AVG</t>
@@ -1297,7 +1300,7 @@
     <t>avg/en-us/vpn-territory</t>
   </si>
   <si>
-    <t>2026-06-19T01:05:21.445Z</t>
+    <t>2026-06-22T17:07:29.046Z</t>
   </si>
   <si>
     <t>VPN Territory</t>
@@ -1312,7 +1315,7 @@
     <t>avg/en-us/windows-10-antivirus</t>
   </si>
   <si>
-    <t>2026-06-19T01:10:08.717Z</t>
+    <t>2026-06-22T18:23:48.779Z</t>
   </si>
   <si>
     <t xml:space="preserve">Download Free Antivirus Software for Windows 10 PC | AVG </t>
@@ -1327,7 +1330,7 @@
     <t>avg/en-us/windows-11-antivirus</t>
   </si>
   <si>
-    <t>2026-06-19T01:11:00.635Z</t>
+    <t>2026-06-22T18:25:07.882Z</t>
   </si>
   <si>
     <t xml:space="preserve">Download AVG AntiVirus FREE for Windows 11 PCs | AVG </t>
@@ -1345,7 +1348,7 @@
     <t>avg/en-us/windows-7-antivirus</t>
   </si>
   <si>
-    <t>2026-06-19T01:11:53.501Z</t>
+    <t>2026-06-22T18:26:02.247Z</t>
   </si>
   <si>
     <t>Free Antivirus for Windows 7 | PC Virus Scan Software | AVG</t>
@@ -1360,7 +1363,7 @@
     <t>avg/en-us/windows-8-antivirus</t>
   </si>
   <si>
-    <t>2026-06-19T01:12:46.007Z</t>
+    <t>2026-06-22T18:26:56.655Z</t>
   </si>
   <si>
     <t>Antivirus for Windows 8 | AVG Free Download</t>
@@ -1375,7 +1378,7 @@
     <t>avg/en-us/affiliate/become-an-avg-affiliate</t>
   </si>
   <si>
-    <t>2026-06-19T00:49:48.943Z</t>
+    <t>2026-06-22T15:55:27.654Z</t>
   </si>
   <si>
     <t>Become an AVG affiliate</t>
@@ -1390,7 +1393,7 @@
     <t>avg/en-us/campaign-landing-pages/ransomware-infographic-download</t>
   </si>
   <si>
-    <t>2026-06-19T00:50:02.544Z</t>
+    <t>2026-06-22T15:55:40.709Z</t>
   </si>
   <si>
     <t>https://www.avg.com/en-us/campaign-landing-pages/ransomware-infographic-download</t>
@@ -1402,7 +1405,7 @@
     <t>avg/en-us/campaign-landing-pages/ransomware-kit-download</t>
   </si>
   <si>
-    <t>2026-06-19T00:50:09.032Z</t>
+    <t>2026-06-22T15:55:46.968Z</t>
   </si>
   <si>
     <t>https://www.avg.com/en-us/campaign-landing-pages/ransomware-kit-download</t>
@@ -1414,7 +1417,7 @@
     <t>avg/en-us/privacy/updates</t>
   </si>
   <si>
-    <t>2026-06-19T00:56:22.560Z</t>
+    <t>2026-06-22T16:54:36.698Z</t>
   </si>
   <si>
     <t>https://www.avg.com/en-us/privacy/updates</t>
@@ -2028,10 +2031,10 @@
         <v>51</v>
       </c>
       <c r="B9" t="s">
-        <v>35</v>
+        <v>52</v>
       </c>
       <c r="C9" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D9" t="s">
         <v>11</v>
@@ -2040,24 +2043,24 @@
         <v>24</v>
       </c>
       <c r="F9" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G9" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H9" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B10" t="s">
         <v>9</v>
       </c>
       <c r="C10" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D10" t="s">
         <v>11</v>
@@ -2066,24 +2069,24 @@
         <v>18</v>
       </c>
       <c r="F10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H10" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B11" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C11" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D11" t="s">
         <v>11</v>
@@ -2092,24 +2095,24 @@
         <v>24</v>
       </c>
       <c r="F11" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G11" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H11" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B12" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C12" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D12" t="s">
         <v>11</v>
@@ -2118,24 +2121,24 @@
         <v>24</v>
       </c>
       <c r="F12" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G12" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H12" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B13" t="s">
         <v>9</v>
       </c>
       <c r="C13" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D13" t="s">
         <v>11</v>
@@ -2144,24 +2147,24 @@
         <v>24</v>
       </c>
       <c r="F13" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G13" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H13" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C14" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D14" t="s">
         <v>11</v>
@@ -2170,24 +2173,24 @@
         <v>24</v>
       </c>
       <c r="F14" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G14" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H14" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B15" t="s">
-        <v>22</v>
+        <v>86</v>
       </c>
       <c r="C15" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D15" t="s">
         <v>11</v>
@@ -2196,50 +2199,50 @@
         <v>24</v>
       </c>
       <c r="F15" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="G15" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="H15" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B16" t="s">
         <v>9</v>
       </c>
       <c r="C16" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D16" t="s">
         <v>11</v>
       </c>
       <c r="E16" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="F16" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G16" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="H16" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B17" t="s">
-        <v>22</v>
+        <v>86</v>
       </c>
       <c r="C17" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D17" t="s">
         <v>11</v>
@@ -2248,24 +2251,24 @@
         <v>24</v>
       </c>
       <c r="F17" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="G17" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H17" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B18" t="s">
         <v>9</v>
       </c>
       <c r="C18" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D18" t="s">
         <v>11</v>
@@ -2274,24 +2277,24 @@
         <v>12</v>
       </c>
       <c r="F18" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="G18" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="H18" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B19" t="s">
         <v>22</v>
       </c>
       <c r="C19" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D19" t="s">
         <v>11</v>
@@ -2300,24 +2303,24 @@
         <v>24</v>
       </c>
       <c r="F19" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="G19" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="H19" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B20" t="s">
         <v>9</v>
       </c>
       <c r="C20" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D20" t="s">
         <v>11</v>
@@ -2326,24 +2329,24 @@
         <v>30</v>
       </c>
       <c r="F20" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="G20" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="H20" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B21" t="s">
         <v>9</v>
       </c>
       <c r="C21" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D21" t="s">
         <v>11</v>
@@ -2352,24 +2355,24 @@
         <v>30</v>
       </c>
       <c r="F21" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="G21" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="H21" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B22" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C22" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D22" t="s">
         <v>11</v>
@@ -2378,24 +2381,24 @@
         <v>30</v>
       </c>
       <c r="F22" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="G22" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="H22" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B23" t="s">
         <v>9</v>
       </c>
       <c r="C23" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D23" t="s">
         <v>11</v>
@@ -2404,24 +2407,24 @@
         <v>12</v>
       </c>
       <c r="F23" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="G23" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="H23" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B24" t="s">
         <v>9</v>
       </c>
       <c r="C24" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="D24" t="s">
         <v>11</v>
@@ -2430,24 +2433,24 @@
         <v>12</v>
       </c>
       <c r="F24" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="G24" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="H24" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B25" t="s">
         <v>9</v>
       </c>
       <c r="C25" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D25" t="s">
         <v>11</v>
@@ -2456,24 +2459,24 @@
         <v>18</v>
       </c>
       <c r="F25" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="G25" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H25" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B26" t="s">
         <v>9</v>
       </c>
       <c r="C26" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D26" t="s">
         <v>11</v>
@@ -2482,24 +2485,24 @@
         <v>12</v>
       </c>
       <c r="F26" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="G26" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="H26" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B27" t="s">
         <v>9</v>
       </c>
       <c r="C27" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D27" t="s">
         <v>11</v>
@@ -2508,24 +2511,24 @@
         <v>12</v>
       </c>
       <c r="F27" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="G27" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="H27" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B28" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C28" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D28" t="s">
         <v>11</v>
@@ -2534,24 +2537,24 @@
         <v>24</v>
       </c>
       <c r="F28" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="G28" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="H28" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B29" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C29" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D29" t="s">
         <v>11</v>
@@ -2560,24 +2563,24 @@
         <v>24</v>
       </c>
       <c r="F29" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="G29" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="H29" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B30" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C30" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D30" t="s">
         <v>11</v>
@@ -2586,24 +2589,24 @@
         <v>24</v>
       </c>
       <c r="F30" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="G30" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="H30" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B31" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C31" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D31" t="s">
         <v>11</v>
@@ -2612,24 +2615,24 @@
         <v>30</v>
       </c>
       <c r="F31" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="G31" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="H31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B32" t="s">
         <v>9</v>
       </c>
       <c r="C32" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D32" t="s">
         <v>11</v>
@@ -2638,24 +2641,24 @@
         <v>30</v>
       </c>
       <c r="F32" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="G32" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="H32" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B33" t="s">
         <v>9</v>
       </c>
       <c r="C33" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D33" t="s">
         <v>11</v>
@@ -2664,24 +2667,24 @@
         <v>12</v>
       </c>
       <c r="F33" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="G33" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="H33" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B34" t="s">
-        <v>185</v>
+        <v>171</v>
       </c>
       <c r="C34" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D34" t="s">
         <v>11</v>
@@ -2690,24 +2693,24 @@
         <v>30</v>
       </c>
       <c r="F34" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="G34" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H34" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B35" t="s">
-        <v>22</v>
+        <v>86</v>
       </c>
       <c r="C35" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D35" t="s">
         <v>11</v>
@@ -2716,24 +2719,24 @@
         <v>24</v>
       </c>
       <c r="F35" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="G35" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H35" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B36" t="s">
         <v>9</v>
       </c>
       <c r="C36" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D36" t="s">
         <v>11</v>
@@ -2742,76 +2745,76 @@
         <v>18</v>
       </c>
       <c r="F36" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G36" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H36" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B37" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C37" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D37" t="s">
         <v>11</v>
       </c>
       <c r="E37" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="F37" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="G37" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H37" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B38" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C38" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D38" t="s">
         <v>11</v>
       </c>
       <c r="E38" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F38" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G38" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H38" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B39" t="s">
         <v>9</v>
       </c>
       <c r="C39" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D39" t="s">
         <v>11</v>
@@ -2820,24 +2823,24 @@
         <v>24</v>
       </c>
       <c r="F39" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G39" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H39" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B40" t="s">
         <v>9</v>
       </c>
       <c r="C40" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D40" t="s">
         <v>11</v>
@@ -2846,24 +2849,24 @@
         <v>30</v>
       </c>
       <c r="F40" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="G40" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H40" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B41" t="s">
         <v>41</v>
       </c>
       <c r="C41" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D41" t="s">
         <v>11</v>
@@ -2872,24 +2875,24 @@
         <v>24</v>
       </c>
       <c r="F41" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G41" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H41" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B42" t="s">
         <v>41</v>
       </c>
       <c r="C42" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="D42" t="s">
         <v>11</v>
@@ -2898,24 +2901,24 @@
         <v>24</v>
       </c>
       <c r="F42" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="G42" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H42" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B43" t="s">
         <v>9</v>
       </c>
       <c r="C43" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D43" t="s">
         <v>11</v>
@@ -2924,24 +2927,24 @@
         <v>18</v>
       </c>
       <c r="F43" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="G43" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H43" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B44" t="s">
         <v>9</v>
       </c>
       <c r="C44" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D44" t="s">
         <v>11</v>
@@ -2950,24 +2953,24 @@
         <v>12</v>
       </c>
       <c r="F44" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="G44" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H44" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B45" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C45" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D45" t="s">
         <v>11</v>
@@ -2976,24 +2979,24 @@
         <v>30</v>
       </c>
       <c r="F45" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="G45" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H45" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B46" t="s">
-        <v>22</v>
+        <v>86</v>
       </c>
       <c r="C46" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D46" t="s">
         <v>11</v>
@@ -3002,102 +3005,102 @@
         <v>24</v>
       </c>
       <c r="F46" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="G46" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="H46" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B47" t="s">
         <v>9</v>
       </c>
       <c r="C47" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D47" t="s">
         <v>11</v>
       </c>
       <c r="E47" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="F47" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="G47" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H47" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B48" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C48" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D48" t="s">
         <v>11</v>
       </c>
       <c r="E48" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="F48" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="G48" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H48" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B49" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C49" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D49" t="s">
         <v>11</v>
       </c>
       <c r="E49" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="F49" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="G49" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H49" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B50" t="s">
         <v>9</v>
       </c>
       <c r="C50" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D50" t="s">
         <v>11</v>
@@ -3106,24 +3109,24 @@
         <v>18</v>
       </c>
       <c r="F50" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="G50" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H50" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B51" t="s">
         <v>9</v>
       </c>
       <c r="C51" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D51" t="s">
         <v>11</v>
@@ -3132,24 +3135,24 @@
         <v>18</v>
       </c>
       <c r="F51" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="G51" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H51" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B52" t="s">
         <v>9</v>
       </c>
       <c r="C52" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D52" t="s">
         <v>11</v>
@@ -3158,24 +3161,24 @@
         <v>30</v>
       </c>
       <c r="F52" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="G52" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H52" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B53" t="s">
         <v>9</v>
       </c>
       <c r="C53" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D53" t="s">
         <v>11</v>
@@ -3184,24 +3187,24 @@
         <v>12</v>
       </c>
       <c r="F53" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="G53" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H53" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B54" t="s">
         <v>9</v>
       </c>
       <c r="C54" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D54" t="s">
         <v>11</v>
@@ -3210,24 +3213,24 @@
         <v>12</v>
       </c>
       <c r="F54" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="G54" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H54" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B55" t="s">
         <v>9</v>
       </c>
       <c r="C55" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D55" t="s">
         <v>11</v>
@@ -3236,24 +3239,24 @@
         <v>12</v>
       </c>
       <c r="F55" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="G55" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H55" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B56" t="s">
         <v>9</v>
       </c>
       <c r="C56" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D56" t="s">
         <v>11</v>
@@ -3262,24 +3265,24 @@
         <v>12</v>
       </c>
       <c r="F56" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="G56" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H56" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B57" t="s">
         <v>9</v>
       </c>
       <c r="C57" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D57" t="s">
         <v>11</v>
@@ -3288,76 +3291,76 @@
         <v>18</v>
       </c>
       <c r="F57" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="G57" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H57" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B58" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C58" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D58" t="s">
         <v>11</v>
       </c>
       <c r="E58" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="F58" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="G58" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H58" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B59" t="s">
         <v>9</v>
       </c>
       <c r="C59" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="D59" t="s">
         <v>11</v>
       </c>
       <c r="E59" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="F59" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="G59" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H59" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B60" t="s">
         <v>9</v>
       </c>
       <c r="C60" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D60" t="s">
         <v>11</v>
@@ -3366,24 +3369,24 @@
         <v>12</v>
       </c>
       <c r="F60" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="G60" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H60" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B61" t="s">
         <v>9</v>
       </c>
       <c r="C61" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D61" t="s">
         <v>11</v>
@@ -3392,24 +3395,24 @@
         <v>18</v>
       </c>
       <c r="F61" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="G61" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H61" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B62" t="s">
         <v>9</v>
       </c>
       <c r="C62" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D62" t="s">
         <v>11</v>
@@ -3418,24 +3421,24 @@
         <v>18</v>
       </c>
       <c r="F62" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="G62" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="H62" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B63" t="s">
         <v>9</v>
       </c>
       <c r="C63" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="D63" t="s">
         <v>11</v>
@@ -3444,24 +3447,24 @@
         <v>18</v>
       </c>
       <c r="F63" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="G63" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H63" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B64" t="s">
         <v>9</v>
       </c>
       <c r="C64" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D64" t="s">
         <v>11</v>
@@ -3470,24 +3473,24 @@
         <v>12</v>
       </c>
       <c r="F64" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="G64" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H64" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B65" t="s">
-        <v>22</v>
+        <v>86</v>
       </c>
       <c r="C65" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D65" t="s">
         <v>11</v>
@@ -3496,24 +3499,24 @@
         <v>24</v>
       </c>
       <c r="F65" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="G65" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="H65" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B66" t="s">
         <v>9</v>
       </c>
       <c r="C66" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D66" t="s">
         <v>11</v>
@@ -3522,24 +3525,24 @@
         <v>12</v>
       </c>
       <c r="F66" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="G66" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="H66" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B67" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C67" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D67" t="s">
         <v>11</v>
@@ -3548,24 +3551,24 @@
         <v>24</v>
       </c>
       <c r="F67" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="G67" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H67" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B68" t="s">
         <v>9</v>
       </c>
       <c r="C68" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="D68" t="s">
         <v>11</v>
@@ -3574,24 +3577,24 @@
         <v>18</v>
       </c>
       <c r="F68" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="G68" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H68" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B69" t="s">
         <v>9</v>
       </c>
       <c r="C69" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="D69" t="s">
         <v>11</v>
@@ -3600,24 +3603,24 @@
         <v>30</v>
       </c>
       <c r="F69" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="G69" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H69" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B70" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C70" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D70" t="s">
         <v>11</v>
@@ -3626,24 +3629,24 @@
         <v>30</v>
       </c>
       <c r="F70" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="G70" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H70" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B71" t="s">
         <v>9</v>
       </c>
       <c r="C71" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="D71" t="s">
         <v>11</v>
@@ -3652,24 +3655,24 @@
         <v>24</v>
       </c>
       <c r="F71" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="G71" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H71" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B72" t="s">
         <v>9</v>
       </c>
       <c r="C72" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="D72" t="s">
         <v>11</v>
@@ -3678,24 +3681,24 @@
         <v>18</v>
       </c>
       <c r="F72" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="G72" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H72" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B73" t="s">
         <v>9</v>
       </c>
       <c r="C73" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="D73" t="s">
         <v>11</v>
@@ -3704,24 +3707,24 @@
         <v>12</v>
       </c>
       <c r="F73" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="G73" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H73" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B74" t="s">
         <v>9</v>
       </c>
       <c r="C74" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D74" t="s">
         <v>11</v>
@@ -3730,24 +3733,24 @@
         <v>12</v>
       </c>
       <c r="F74" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="G74" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H74" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B75" t="s">
         <v>9</v>
       </c>
       <c r="C75" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="D75" t="s">
         <v>11</v>
@@ -3756,24 +3759,24 @@
         <v>12</v>
       </c>
       <c r="F75" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="G75" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="H75" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B76" t="s">
         <v>9</v>
       </c>
       <c r="C76" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="D76" t="s">
         <v>11</v>
@@ -3782,24 +3785,24 @@
         <v>12</v>
       </c>
       <c r="F76" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="G76" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H76" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B77" t="s">
         <v>9</v>
       </c>
       <c r="C77" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="D77" t="s">
         <v>11</v>
@@ -3808,24 +3811,24 @@
         <v>24</v>
       </c>
       <c r="F77" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="G77" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H77" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B78" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C78" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="D78" t="s">
         <v>11</v>
@@ -3834,24 +3837,24 @@
         <v>24</v>
       </c>
       <c r="F78" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="G78" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H78" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B79" t="s">
         <v>9</v>
       </c>
       <c r="C79" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="D79" t="s">
         <v>11</v>
@@ -3860,24 +3863,24 @@
         <v>12</v>
       </c>
       <c r="F79" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="G79" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H79" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B80" t="s">
         <v>9</v>
       </c>
       <c r="C80" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="D80" t="s">
         <v>11</v>
@@ -3886,24 +3889,24 @@
         <v>12</v>
       </c>
       <c r="F80" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="G80" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H80" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B81" t="s">
         <v>9</v>
       </c>
       <c r="C81" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="D81" t="s">
         <v>11</v>
@@ -3912,24 +3915,24 @@
         <v>12</v>
       </c>
       <c r="F81" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="G81" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H81" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B82" t="s">
         <v>9</v>
       </c>
       <c r="C82" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="D82" t="s">
         <v>11</v>
@@ -3938,24 +3941,24 @@
         <v>24</v>
       </c>
       <c r="F82" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="G82" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H82" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B83" t="s">
         <v>9</v>
       </c>
       <c r="C83" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="D83" t="s">
         <v>11</v>
@@ -3964,24 +3967,24 @@
         <v>24</v>
       </c>
       <c r="F83" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="G83" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H83" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B84" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C84" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="D84" t="s">
         <v>11</v>
@@ -3990,24 +3993,24 @@
         <v>24</v>
       </c>
       <c r="F84" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="G84" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H84" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B85" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C85" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="D85" t="s">
         <v>11</v>
@@ -4016,24 +4019,24 @@
         <v>24</v>
       </c>
       <c r="F85" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="G85" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="H85" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B86" t="s">
         <v>9</v>
       </c>
       <c r="C86" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="D86" t="s">
         <v>11</v>
@@ -4042,24 +4045,24 @@
         <v>18</v>
       </c>
       <c r="F86" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="G86" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H86" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B87" t="s">
         <v>9</v>
       </c>
       <c r="C87" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D87" t="s">
         <v>11</v>
@@ -4068,24 +4071,24 @@
         <v>18</v>
       </c>
       <c r="F87" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="G87" t="s">
         <v>14</v>
       </c>
       <c r="H87" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B88" t="s">
         <v>9</v>
       </c>
       <c r="C88" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="D88" t="s">
         <v>11</v>
@@ -4094,24 +4097,24 @@
         <v>18</v>
       </c>
       <c r="F88" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="G88" t="s">
         <v>14</v>
       </c>
       <c r="H88" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B89" t="s">
         <v>9</v>
       </c>
       <c r="C89" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="D89" t="s">
         <v>11</v>
@@ -4120,13 +4123,13 @@
         <v>12</v>
       </c>
       <c r="F89" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="G89" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H89" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
   </sheetData>
